--- a/xls/square_high_un_16_tri3_22.xlsx
+++ b/xls/square_high_un_16_tri3_22.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>668</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>340</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>564</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>3138</v>
+      </c>
+      <c r="I20">
+        <v>-1.4880258490266332</v>
+      </c>
+      <c r="J20">
+        <v>-1.2801581018344836</v>
+      </c>
+      <c r="K20">
+        <v>1.3545779438209273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>668</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>340</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>598</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>3330</v>
+      </c>
+      <c r="I21">
+        <v>-0.8366965701106439</v>
+      </c>
+      <c r="J21">
+        <v>-0.7311953763208661</v>
+      </c>
+      <c r="K21">
+        <v>1.7965761787011596</v>
+      </c>
+    </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
